--- a/JsonConverter/ExcelFiles/Collection.xlsx
+++ b/JsonConverter/ExcelFiles/Collection.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t xml:space="preserve">캐릭터 고유 ID</t>
   </si>
@@ -46,19 +46,61 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
+    <t xml:space="preserve">collection_gem_00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보석</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보석 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Icon/Icon_Obj/Icon_Item/gem-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item</t>
+  </si>
+  <si>
     <t xml:space="preserve">collection_gem_01</t>
   </si>
   <si>
-    <t xml:space="preserve">보석</t>
-  </si>
-  <si>
-    <t xml:space="preserve">보석 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Icon/Icon_Obj/Icon_Item/gem-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item</t>
+    <t xml:space="preserve">보석 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collection_gem_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보석 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collection_gem_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보석 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collection_gem_04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보석 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collection_gem_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보석 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collection_gem_06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보석 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collection_gem_07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보석 8</t>
   </si>
 </sst>
 </file>
@@ -69,7 +111,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -122,13 +164,6 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
   </fonts>
   <fills count="4">
@@ -192,7 +227,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -239,10 +274,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -582,11 +613,19 @@
       <c r="N4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="12"/>
+      <c r="A5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
+      <c r="E5" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
@@ -598,11 +637,19 @@
       <c r="N5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
+      <c r="A6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
+      <c r="E6" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
@@ -614,11 +661,19 @@
       <c r="N6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
+      <c r="A7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
+      <c r="E7" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
@@ -630,11 +685,19 @@
       <c r="N7" s="11"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
+      <c r="A8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
+      <c r="E8" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
@@ -646,11 +709,19 @@
       <c r="N8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
+      <c r="A9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
+      <c r="E9" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
@@ -662,11 +733,19 @@
       <c r="N9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
+      <c r="E10" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
@@ -678,11 +757,19 @@
       <c r="N10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
+      <c r="A11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
+      <c r="E11" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
